--- a/static/files/lista_vehicule_20250602.xlsx
+++ b/static/files/lista_vehicule_20250602.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNB-IT\Documents\code\pnb_main\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8DC782-5B5B-4DE3-AFC8-7FAAF889E5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F11BC52-2102-443B-A900-9B632C843AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="nSJtxeG/aruAKHEluz0lCESAJmzZCuFE10n/CQktNAqqpuTo7ovEnd1c2ySeqVBYja4IS2AjtBpC6gNj+cXKtA==" workbookSaltValue="rU5aWuRwxjE0fcDPyndx4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CDE1514B-66A0-46CC-B6F9-1E7EE8F061CC}"/>
